--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N227_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N227_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57610429783734</v>
+        <v>1.718616948398568</v>
       </c>
       <c r="D2" t="n">
-        <v>15.4237054288019</v>
+        <v>2.506352132180308</v>
       </c>
       <c r="E2" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F2" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.21798409589366</v>
+        <v>9.785422415582721</v>
       </c>
       <c r="D3" t="n">
-        <v>32.23030588635717</v>
+        <v>5.237424706533041</v>
       </c>
       <c r="E3" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F3" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.89862812067054</v>
+        <v>5.833527069608962</v>
       </c>
       <c r="D4" t="n">
-        <v>30.07876491422865</v>
+        <v>4.887799298562155</v>
       </c>
       <c r="E4" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F4" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.8359598671335</v>
+        <v>5.010843478409194</v>
       </c>
       <c r="D5" t="n">
-        <v>25.1632202692936</v>
+        <v>4.089023293760209</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F5" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.00054122360372</v>
+        <v>6.500087948835604</v>
       </c>
       <c r="D6" t="n">
-        <v>27.56837739328823</v>
+        <v>4.479861326409337</v>
       </c>
       <c r="E6" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F6" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.74824834624064</v>
+        <v>6.621590356264104</v>
       </c>
       <c r="D7" t="n">
-        <v>13.80510469206231</v>
+        <v>2.243329512460126</v>
       </c>
       <c r="E7" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F7" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.58562716344523</v>
+        <v>5.457664414059851</v>
       </c>
       <c r="D8" t="n">
-        <v>10.89795540910153</v>
+        <v>1.770917753978999</v>
       </c>
       <c r="E8" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F8" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.41210026675497</v>
+        <v>3.641966293347683</v>
       </c>
       <c r="D9" t="n">
-        <v>24.5615086411184</v>
+        <v>3.991245154181741</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F9" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.3709055220974</v>
+        <v>2.985272147340828</v>
       </c>
       <c r="D10" t="n">
-        <v>22.26293853192254</v>
+        <v>3.617727511437413</v>
       </c>
       <c r="E10" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F10" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.83376269004362</v>
+        <v>7.772986437132088</v>
       </c>
       <c r="D11" t="n">
-        <v>15.8113883008419</v>
+        <v>2.569350598886808</v>
       </c>
       <c r="E11" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F11" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.5031152513486</v>
+        <v>3.331756228344148</v>
       </c>
       <c r="D12" t="n">
-        <v>19.4001706574654</v>
+        <v>3.152527731838128</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F12" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.71135418962533</v>
+        <v>5.640595055814117</v>
       </c>
       <c r="D13" t="n">
-        <v>22.85147980610215</v>
+        <v>3.7133654684916</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F13" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.50886476761107</v>
+        <v>5.6076905247368</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80771712157776</v>
+        <v>4.843754032256386</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F14" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>64.05910335362881</v>
+        <v>10.40960429496468</v>
       </c>
       <c r="D15" t="n">
-        <v>11.88486432400471</v>
+        <v>1.931290452650766</v>
       </c>
       <c r="E15" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F15" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.39750175940008</v>
+        <v>3.639594035902514</v>
       </c>
       <c r="D16" t="n">
-        <v>17.17261808198546</v>
+        <v>2.790550438322637</v>
       </c>
       <c r="E16" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F16" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.577768231494</v>
+        <v>4.806387337617775</v>
       </c>
       <c r="D17" t="n">
-        <v>27.97795431138745</v>
+        <v>4.546417575600461</v>
       </c>
       <c r="E17" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F17" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>43.54495552840218</v>
+        <v>7.076055273365355</v>
       </c>
       <c r="D18" t="n">
-        <v>28.86684919936642</v>
+        <v>4.690862994897044</v>
       </c>
       <c r="E18" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F18" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.23015727212251</v>
+        <v>3.449900556719908</v>
       </c>
       <c r="D19" t="n">
-        <v>20.76269749624708</v>
+        <v>3.37393834314015</v>
       </c>
       <c r="E19" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F19" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>43.70933300150455</v>
+        <v>7.102766612744491</v>
       </c>
       <c r="D20" t="n">
-        <v>36.04249899599343</v>
+        <v>5.856906086848933</v>
       </c>
       <c r="E20" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F20" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>18.78165511943842</v>
+        <v>3.052018956908743</v>
       </c>
       <c r="D21" t="n">
-        <v>12.0069747335045</v>
+        <v>1.951133394194482</v>
       </c>
       <c r="E21" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F21" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>22.83495025757929</v>
+        <v>3.710679416856634</v>
       </c>
       <c r="D22" t="n">
-        <v>22.48785358872158</v>
+        <v>3.654276208167257</v>
       </c>
       <c r="E22" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F22" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>9.191979302067786</v>
+        <v>1.493696636586015</v>
       </c>
       <c r="D23" t="n">
-        <v>5.544002638641785</v>
+        <v>0.90090042877929</v>
       </c>
       <c r="E23" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F23" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>13.06043953874171</v>
+        <v>2.122321425045528</v>
       </c>
       <c r="D24" t="n">
-        <v>10.1096592182358</v>
+        <v>1.642819622963318</v>
       </c>
       <c r="E24" t="n">
-        <v>14.3341535014324</v>
+        <v>2.329299943982764</v>
       </c>
       <c r="F24" t="n">
-        <v>7.950706615725506</v>
+        <v>1.291989825055395</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
